--- a/個人別_作業達成度と改善分析_v6.xlsx
+++ b/個人別_作業達成度と改善分析_v6.xlsx
@@ -8666,7 +8666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -8676,6 +8676,7 @@
     <col min="10" max="10" width="18.7109375" customWidth="1"/>
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="13" width="0" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8763,7 +8764,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="34" customHeight="1">
+    <row r="8" spans="1:14" ht="34" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>9</v>
       </c>
@@ -8803,8 +8804,13 @@
       <c r="M8" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>表示順キー</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -8853,8 +8859,12 @@
         <f>IF(OR(E9="",E9=0),-1E+99,F9-ROW()/100000)</f>
         <v>1.1551446570397113</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" s="9">
+        <f>IF(B9="","",COUNTA($B$9:B9))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="8">
         <v>2</v>
       </c>
@@ -8903,8 +8913,12 @@
         <f>IF(OR(E10="",E10=0),-1E+99,F10-ROW()/100000)</f>
         <v>1.0737255033557047</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="9">
+        <f>IF(B10="","",COUNTA($B$9:B10))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="8">
         <v>3</v>
       </c>
@@ -8953,8 +8967,12 @@
         <f>IF(OR(E11="",E11=0),-1E+99,F11-ROW()/100000)</f>
         <v>1.0157630158730158</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="9">
+        <f>IF(B11="","",COUNTA($B$9:B11))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="8">
         <v>4</v>
       </c>
@@ -9003,8 +9021,12 @@
         <f>IF(OR(E12="",E12=0),-1E+99,F12-ROW()/100000)</f>
         <v>1.0093437223974766</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12" s="9">
+        <f>IF(B12="","",COUNTA($B$9:B12))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="8">
         <v>5</v>
       </c>
@@ -9053,8 +9075,12 @@
         <f>IF(OR(E13="",E13=0),-1E+99,F13-ROW()/100000)</f>
         <v>0.9550938805970152</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" s="9">
+        <f>IF(B13="","",COUNTA($B$9:B13))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="8">
         <v>6</v>
       </c>
@@ -9103,8 +9129,12 @@
         <f>IF(OR(E14="",E14=0),-1E+99,F14-ROW()/100000)</f>
         <v>0.9550838805970149</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" s="9">
+        <f>IF(B14="","",COUNTA($B$9:B14))</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="8">
         <v>7</v>
       </c>
@@ -9153,8 +9183,12 @@
         <f>IF(OR(E15="",E15=0),-1E+99,F15-ROW()/100000)</f>
         <v>0.9410264705882353</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" s="9">
+        <f>IF(B15="","",COUNTA($B$9:B15))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="8">
         <v>8</v>
       </c>
@@ -9203,8 +9237,12 @@
         <f>IF(OR(E16="",E16=0),-1E+99,F16-ROW()/100000)</f>
         <v>0.8531733333333333</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="9">
+        <f>IF(B16="","",COUNTA($B$9:B16))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="8">
         <v>9</v>
       </c>
@@ -9247,8 +9285,12 @@
         <f>IF(OR(E17="",E17=0),-1E+99,F17-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="9" t="str">
+        <f>IF(B17="","",COUNTA($B$9:B17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="8">
         <v>10</v>
       </c>
@@ -9291,8 +9333,12 @@
         <f>IF(OR(E18="",E18=0),-1E+99,F18-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="9" t="str">
+        <f>IF(B18="","",COUNTA($B$9:B18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="8">
         <v>11</v>
       </c>
@@ -9335,8 +9381,12 @@
         <f>IF(OR(E19="",E19=0),-1E+99,F19-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="9" t="str">
+        <f>IF(B19="","",COUNTA($B$9:B19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="8">
         <v>12</v>
       </c>
@@ -9379,8 +9429,12 @@
         <f>IF(OR(E20="",E20=0),-1E+99,F20-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="9" t="str">
+        <f>IF(B20="","",COUNTA($B$9:B20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="8">
         <v>13</v>
       </c>
@@ -9423,8 +9477,12 @@
         <f>IF(OR(E21="",E21=0),-1E+99,F21-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="9" t="str">
+        <f>IF(B21="","",COUNTA($B$9:B21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="8">
         <v>14</v>
       </c>
@@ -9467,8 +9525,12 @@
         <f>IF(OR(E22="",E22=0),-1E+99,F22-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="9" t="str">
+        <f>IF(B22="","",COUNTA($B$9:B22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="8">
         <v>15</v>
       </c>
@@ -9511,8 +9573,12 @@
         <f>IF(OR(E23="",E23=0),-1E+99,F23-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="9" t="str">
+        <f>IF(B23="","",COUNTA($B$9:B23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="8">
         <v>16</v>
       </c>
@@ -9555,8 +9621,12 @@
         <f>IF(OR(E24="",E24=0),-1E+99,F24-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="9" t="str">
+        <f>IF(B24="","",COUNTA($B$9:B24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="8">
         <v>17</v>
       </c>
@@ -9599,8 +9669,12 @@
         <f>IF(OR(E25="",E25=0),-1E+99,F25-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="9" t="str">
+        <f>IF(B25="","",COUNTA($B$9:B25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="8">
         <v>18</v>
       </c>
@@ -9643,8 +9717,12 @@
         <f>IF(OR(E26="",E26=0),-1E+99,F26-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="9" t="str">
+        <f>IF(B26="","",COUNTA($B$9:B26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="8">
         <v>19</v>
       </c>
@@ -9687,8 +9765,12 @@
         <f>IF(OR(E27="",E27=0),-1E+99,F27-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="9" t="str">
+        <f>IF(B27="","",COUNTA($B$9:B27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="8">
         <v>20</v>
       </c>
@@ -9731,8 +9813,12 @@
         <f>IF(OR(E28="",E28=0),-1E+99,F28-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="9" t="str">
+        <f>IF(B28="","",COUNTA($B$9:B28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="8">
         <v>21</v>
       </c>
@@ -9775,8 +9861,12 @@
         <f>IF(OR(E29="",E29=0),-1E+99,F29-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="9" t="str">
+        <f>IF(B29="","",COUNTA($B$9:B29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="8">
         <v>22</v>
       </c>
@@ -9819,8 +9909,12 @@
         <f>IF(OR(E30="",E30=0),-1E+99,F30-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="9" t="str">
+        <f>IF(B30="","",COUNTA($B$9:B30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="8">
         <v>23</v>
       </c>
@@ -9863,8 +9957,12 @@
         <f>IF(OR(E31="",E31=0),-1E+99,F31-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="9" t="str">
+        <f>IF(B31="","",COUNTA($B$9:B31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="8">
         <v>24</v>
       </c>
@@ -9907,8 +10005,12 @@
         <f>IF(OR(E32="",E32=0),-1E+99,F32-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="9" t="str">
+        <f>IF(B32="","",COUNTA($B$9:B32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="8">
         <v>25</v>
       </c>
@@ -9951,8 +10053,12 @@
         <f>IF(OR(E33="",E33=0),-1E+99,F33-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="9" t="str">
+        <f>IF(B33="","",COUNTA($B$9:B33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="8">
         <v>26</v>
       </c>
@@ -9995,8 +10101,12 @@
         <f>IF(OR(E34="",E34=0),-1E+99,F34-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" s="9" t="str">
+        <f>IF(B34="","",COUNTA($B$9:B34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="8">
         <v>27</v>
       </c>
@@ -10039,8 +10149,12 @@
         <f>IF(OR(E35="",E35=0),-1E+99,F35-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" s="9" t="str">
+        <f>IF(B35="","",COUNTA($B$9:B35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="8">
         <v>28</v>
       </c>
@@ -10083,8 +10197,12 @@
         <f>IF(OR(E36="",E36=0),-1E+99,F36-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36" s="9" t="str">
+        <f>IF(B36="","",COUNTA($B$9:B36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="8">
         <v>29</v>
       </c>
@@ -10127,8 +10245,12 @@
         <f>IF(OR(E37="",E37=0),-1E+99,F37-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37" s="9" t="str">
+        <f>IF(B37="","",COUNTA($B$9:B37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="8">
         <v>30</v>
       </c>
@@ -10171,8 +10293,12 @@
         <f>IF(OR(E38="",E38=0),-1E+99,F38-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38" s="9" t="str">
+        <f>IF(B38="","",COUNTA($B$9:B38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="8">
         <v>31</v>
       </c>
@@ -10215,8 +10341,12 @@
         <f>IF(OR(E39="",E39=0),-1E+99,F39-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39" s="9" t="str">
+        <f>IF(B39="","",COUNTA($B$9:B39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="8">
         <v>32</v>
       </c>
@@ -10259,8 +10389,12 @@
         <f>IF(OR(E40="",E40=0),-1E+99,F40-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40" s="9" t="str">
+        <f>IF(B40="","",COUNTA($B$9:B40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="8">
         <v>33</v>
       </c>
@@ -10303,8 +10437,12 @@
         <f>IF(OR(E41="",E41=0),-1E+99,F41-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" s="9" t="str">
+        <f>IF(B41="","",COUNTA($B$9:B41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="8">
         <v>34</v>
       </c>
@@ -10347,8 +10485,12 @@
         <f>IF(OR(E42="",E42=0),-1E+99,F42-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42" s="9" t="str">
+        <f>IF(B42="","",COUNTA($B$9:B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="8">
         <v>35</v>
       </c>
@@ -10391,8 +10533,12 @@
         <f>IF(OR(E43="",E43=0),-1E+99,F43-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43" s="9" t="str">
+        <f>IF(B43="","",COUNTA($B$9:B43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="8">
         <v>36</v>
       </c>
@@ -10435,8 +10581,12 @@
         <f>IF(OR(E44="",E44=0),-1E+99,F44-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44" s="9" t="str">
+        <f>IF(B44="","",COUNTA($B$9:B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="8">
         <v>37</v>
       </c>
@@ -10479,8 +10629,12 @@
         <f>IF(OR(E45="",E45=0),-1E+99,F45-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45" s="9" t="str">
+        <f>IF(B45="","",COUNTA($B$9:B45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="8">
         <v>38</v>
       </c>
@@ -10523,8 +10677,12 @@
         <f>IF(OR(E46="",E46=0),-1E+99,F46-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46" s="9" t="str">
+        <f>IF(B46="","",COUNTA($B$9:B46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="8">
         <v>39</v>
       </c>
@@ -10567,8 +10725,12 @@
         <f>IF(OR(E47="",E47=0),-1E+99,F47-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47" s="9" t="str">
+        <f>IF(B47="","",COUNTA($B$9:B47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="8">
         <v>40</v>
       </c>
@@ -10611,8 +10773,12 @@
         <f>IF(OR(E48="",E48=0),-1E+99,F48-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" s="9" t="str">
+        <f>IF(B48="","",COUNTA($B$9:B48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="8">
         <v>41</v>
       </c>
@@ -10655,8 +10821,12 @@
         <f>IF(OR(E49="",E49=0),-1E+99,F49-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49" s="9" t="str">
+        <f>IF(B49="","",COUNTA($B$9:B49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="8">
         <v>42</v>
       </c>
@@ -10699,8 +10869,12 @@
         <f>IF(OR(E50="",E50=0),-1E+99,F50-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50" s="9" t="str">
+        <f>IF(B50="","",COUNTA($B$9:B50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="8">
         <v>43</v>
       </c>
@@ -10743,8 +10917,12 @@
         <f>IF(OR(E51="",E51=0),-1E+99,F51-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51" s="9" t="str">
+        <f>IF(B51="","",COUNTA($B$9:B51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="8">
         <v>44</v>
       </c>
@@ -10787,8 +10965,12 @@
         <f>IF(OR(E52="",E52=0),-1E+99,F52-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="N52" s="9" t="str">
+        <f>IF(B52="","",COUNTA($B$9:B52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="8">
         <v>45</v>
       </c>
@@ -10831,8 +11013,12 @@
         <f>IF(OR(E53="",E53=0),-1E+99,F53-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="N53" s="9" t="str">
+        <f>IF(B53="","",COUNTA($B$9:B53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="8">
         <v>46</v>
       </c>
@@ -10875,8 +11061,12 @@
         <f>IF(OR(E54="",E54=0),-1E+99,F54-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="N54" s="9" t="str">
+        <f>IF(B54="","",COUNTA($B$9:B54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="8">
         <v>47</v>
       </c>
@@ -10919,8 +11109,12 @@
         <f>IF(OR(E55="",E55=0),-1E+99,F55-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="N55" s="9" t="str">
+        <f>IF(B55="","",COUNTA($B$9:B55))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="8">
         <v>48</v>
       </c>
@@ -10963,8 +11157,12 @@
         <f>IF(OR(E56="",E56=0),-1E+99,F56-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="57" spans="1:13">
+      <c r="N56" s="9" t="str">
+        <f>IF(B56="","",COUNTA($B$9:B56))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="8">
         <v>49</v>
       </c>
@@ -11007,8 +11205,12 @@
         <f>IF(OR(E57="",E57=0),-1E+99,F57-ROW()/100000)</f>
         <v>-1E+99</v>
       </c>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="N57" s="9" t="str">
+        <f>IF(B57="","",COUNTA($B$9:B57))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="8">
         <v>50</v>
       </c>
@@ -11050,6 +11252,10 @@
       <c r="M58" s="9">
         <f>IF(OR(E58="",E58=0),-1E+99,F58-ROW()/100000)</f>
         <v>-1E+99</v>
+      </c>
+      <c r="N58" s="9" t="str">
+        <f>IF(B58="","",COUNTA($B$9:B58))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -11251,15 +11457,15 @@
         <v>2.77</v>
       </c>
       <c r="Z2">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z2)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>1</v>
       </c>
       <c r="AA2">
-        <f>IF(ROWS($AA$2:AA2)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA2)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>8</v>
       </c>
       <c r="AB2">
-        <f>IF(ROWS($AB$2:AB2)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB2)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>1</v>
       </c>
       <c r="AC2">
@@ -11363,15 +11569,15 @@
         <v>2.98</v>
       </c>
       <c r="Z3">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z3)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>2</v>
       </c>
       <c r="AA3">
-        <f>IF(ROWS($AA$2:AA3)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA3)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>7</v>
       </c>
       <c r="AB3">
-        <f>IF(ROWS($AB$2:AB3)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB3)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>2</v>
       </c>
       <c r="AC3">
@@ -11475,15 +11681,15 @@
         <v>3.1500000000000004</v>
       </c>
       <c r="Z4">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z4)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>3</v>
       </c>
       <c r="AA4">
-        <f>IF(ROWS($AA$2:AA4)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA4)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>6</v>
       </c>
       <c r="AB4">
-        <f>IF(ROWS($AB$2:AB4)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB4)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>3</v>
       </c>
       <c r="AC4">
@@ -11573,15 +11779,15 @@
         <v>3.17</v>
       </c>
       <c r="Z5">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z5)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>4</v>
       </c>
       <c r="AA5">
-        <f>IF(ROWS($AA$2:AA5)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA5)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>5</v>
       </c>
       <c r="AB5">
-        <f>IF(ROWS($AB$2:AB5)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB5)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>4</v>
       </c>
       <c r="AC5">
@@ -11671,15 +11877,15 @@
         <v>3.3499999999999996</v>
       </c>
       <c r="Z6">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z6)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>5</v>
       </c>
       <c r="AA6">
-        <f>IF(ROWS($AA$2:AA6)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA6)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>4</v>
       </c>
       <c r="AB6">
-        <f>IF(ROWS($AB$2:AB6)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB6)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>5</v>
       </c>
       <c r="AC6">
@@ -11769,15 +11975,15 @@
         <v>3.35</v>
       </c>
       <c r="Z7">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z7)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>6</v>
       </c>
       <c r="AA7">
-        <f>IF(ROWS($AA$2:AA7)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA7)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>3</v>
       </c>
       <c r="AB7">
-        <f>IF(ROWS($AB$2:AB7)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB7)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>6</v>
       </c>
       <c r="AC7">
@@ -11867,15 +12073,15 @@
         <v>3.4000000000000004</v>
       </c>
       <c r="Z8">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z8)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>7</v>
       </c>
       <c r="AA8">
-        <f>IF(ROWS($AA$2:AA8)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA8)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>2</v>
       </c>
       <c r="AB8">
-        <f>IF(ROWS($AB$2:AB8)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB8)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>7</v>
       </c>
       <c r="AC8">
@@ -11965,15 +12171,15 @@
         <v>3.75</v>
       </c>
       <c r="Z9">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z9)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v>8</v>
       </c>
       <c r="AA9">
-        <f>IF(ROWS($AA$2:AA9)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA9)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v>1</v>
       </c>
       <c r="AB9">
-        <f>IF(ROWS($AB$2:AB9)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB9)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v>8</v>
       </c>
       <c r="AC9">
@@ -12063,15 +12269,15 @@
         <v/>
       </c>
       <c r="Z10" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z10)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA10" t="str">
-        <f>IF(ROWS($AA$2:AA10)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA10)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB10" t="str">
-        <f>IF(ROWS($AB$2:AB10)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB10)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC10">
@@ -12161,15 +12367,15 @@
         <v/>
       </c>
       <c r="Z11" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z11)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA11" t="str">
-        <f>IF(ROWS($AA$2:AA11)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA11)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB11" t="str">
-        <f>IF(ROWS($AB$2:AB11)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB11)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC11">
@@ -12259,15 +12465,15 @@
         <v/>
       </c>
       <c r="Z12" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z12)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA12" t="str">
-        <f>IF(ROWS($AA$2:AA12)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA12)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB12" t="str">
-        <f>IF(ROWS($AB$2:AB12)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB12)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC12">
@@ -12357,15 +12563,15 @@
         <v/>
       </c>
       <c r="Z13" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z13)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA13" t="str">
-        <f>IF(ROWS($AA$2:AA13)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA13)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB13" t="str">
-        <f>IF(ROWS($AB$2:AB13)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB13)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC13">
@@ -12455,15 +12661,15 @@
         <v/>
       </c>
       <c r="Z14" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z14)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA14" t="str">
-        <f>IF(ROWS($AA$2:AA14)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA14)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB14" t="str">
-        <f>IF(ROWS($AB$2:AB14)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB14)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC14">
@@ -12553,15 +12759,15 @@
         <v/>
       </c>
       <c r="Z15" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z15)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA15" t="str">
-        <f>IF(ROWS($AA$2:AA15)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA15)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB15" t="str">
-        <f>IF(ROWS($AB$2:AB15)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB15)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC15">
@@ -12651,15 +12857,15 @@
         <v/>
       </c>
       <c r="Z16" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z16)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA16" t="str">
-        <f>IF(ROWS($AA$2:AA16)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA16)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB16" t="str">
-        <f>IF(ROWS($AB$2:AB16)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB16)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC16">
@@ -12749,15 +12955,15 @@
         <v/>
       </c>
       <c r="Z17" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z17)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA17" t="str">
-        <f>IF(ROWS($AA$2:AA17)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA17)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB17" t="str">
-        <f>IF(ROWS($AB$2:AB17)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB17)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC17">
@@ -12847,15 +13053,15 @@
         <v/>
       </c>
       <c r="Z18" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z18)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA18" t="str">
-        <f>IF(ROWS($AA$2:AA18)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA18)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB18" t="str">
-        <f>IF(ROWS($AB$2:AB18)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB18)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC18">
@@ -12945,15 +13151,15 @@
         <v/>
       </c>
       <c r="Z19" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z19)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA19" t="str">
-        <f>IF(ROWS($AA$2:AA19)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA19)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB19" t="str">
-        <f>IF(ROWS($AB$2:AB19)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB19)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC19">
@@ -13043,15 +13249,15 @@
         <v/>
       </c>
       <c r="Z20" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z20)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA20" t="str">
-        <f>IF(ROWS($AA$2:AA20)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA20)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB20" t="str">
-        <f>IF(ROWS($AB$2:AB20)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB20)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC20">
@@ -13141,15 +13347,15 @@
         <v/>
       </c>
       <c r="Z21" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z21)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA21" t="str">
-        <f>IF(ROWS($AA$2:AA21)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA21)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB21" t="str">
-        <f>IF(ROWS($AB$2:AB21)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB21)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC21">
@@ -13239,15 +13445,15 @@
         <v/>
       </c>
       <c r="Z22" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z22)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA22" t="str">
-        <f>IF(ROWS($AA$2:AA22)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA22)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB22" t="str">
-        <f>IF(ROWS($AB$2:AB22)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB22)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC22">
@@ -13337,15 +13543,15 @@
         <v/>
       </c>
       <c r="Z23" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z23)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA23" t="str">
-        <f>IF(ROWS($AA$2:AA23)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA23)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB23" t="str">
-        <f>IF(ROWS($AB$2:AB23)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB23)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC23">
@@ -13435,15 +13641,15 @@
         <v/>
       </c>
       <c r="Z24" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z24)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA24" t="str">
-        <f>IF(ROWS($AA$2:AA24)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA24)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB24" t="str">
-        <f>IF(ROWS($AB$2:AB24)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB24)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC24">
@@ -13533,15 +13739,15 @@
         <v/>
       </c>
       <c r="Z25" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z25)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA25" t="str">
-        <f>IF(ROWS($AA$2:AA25)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA25)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB25" t="str">
-        <f>IF(ROWS($AB$2:AB25)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB25)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC25">
@@ -13631,15 +13837,15 @@
         <v/>
       </c>
       <c r="Z26" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z26)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA26" t="str">
-        <f>IF(ROWS($AA$2:AA26)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA26)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB26" t="str">
-        <f>IF(ROWS($AB$2:AB26)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB26)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC26">
@@ -13729,15 +13935,15 @@
         <v/>
       </c>
       <c r="Z27" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z27)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA27" t="str">
-        <f>IF(ROWS($AA$2:AA27)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA27)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB27" t="str">
-        <f>IF(ROWS($AB$2:AB27)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB27)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC27">
@@ -13827,15 +14033,15 @@
         <v/>
       </c>
       <c r="Z28" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z28)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA28" t="str">
-        <f>IF(ROWS($AA$2:AA28)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA28)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB28" t="str">
-        <f>IF(ROWS($AB$2:AB28)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB28)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC28">
@@ -13925,15 +14131,15 @@
         <v/>
       </c>
       <c r="Z29" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z29)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA29" t="str">
-        <f>IF(ROWS($AA$2:AA29)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA29)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB29" t="str">
-        <f>IF(ROWS($AB$2:AB29)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB29)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC29">
@@ -14023,15 +14229,15 @@
         <v/>
       </c>
       <c r="Z30" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z30)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA30" t="str">
-        <f>IF(ROWS($AA$2:AA30)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA30)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB30" t="str">
-        <f>IF(ROWS($AB$2:AB30)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB30)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC30">
@@ -14121,15 +14327,15 @@
         <v/>
       </c>
       <c r="Z31" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z31)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA31" t="str">
-        <f>IF(ROWS($AA$2:AA31)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA31)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB31" t="str">
-        <f>IF(ROWS($AB$2:AB31)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB31)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC31">
@@ -14219,15 +14425,15 @@
         <v/>
       </c>
       <c r="Z32" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z32)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA32" t="str">
-        <f>IF(ROWS($AA$2:AA32)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA32)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB32" t="str">
-        <f>IF(ROWS($AB$2:AB32)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB32)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC32">
@@ -14317,15 +14523,15 @@
         <v/>
       </c>
       <c r="Z33" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z33)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA33" t="str">
-        <f>IF(ROWS($AA$2:AA33)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA33)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB33" t="str">
-        <f>IF(ROWS($AB$2:AB33)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB33)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC33">
@@ -14415,15 +14621,15 @@
         <v/>
       </c>
       <c r="Z34" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z34)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA34" t="str">
-        <f>IF(ROWS($AA$2:AA34)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA34)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB34" t="str">
-        <f>IF(ROWS($AB$2:AB34)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB34)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC34">
@@ -14513,15 +14719,15 @@
         <v/>
       </c>
       <c r="Z35" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z35)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA35" t="str">
-        <f>IF(ROWS($AA$2:AA35)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA35)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB35" t="str">
-        <f>IF(ROWS($AB$2:AB35)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB35)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC35">
@@ -14611,15 +14817,15 @@
         <v/>
       </c>
       <c r="Z36" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z36)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA36" t="str">
-        <f>IF(ROWS($AA$2:AA36)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA36)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB36" t="str">
-        <f>IF(ROWS($AB$2:AB36)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB36)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC36">
@@ -14709,15 +14915,15 @@
         <v/>
       </c>
       <c r="Z37" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z37)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA37" t="str">
-        <f>IF(ROWS($AA$2:AA37)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA37)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB37" t="str">
-        <f>IF(ROWS($AB$2:AB37)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB37)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC37">
@@ -14807,15 +15013,15 @@
         <v/>
       </c>
       <c r="Z38" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z38)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA38" t="str">
-        <f>IF(ROWS($AA$2:AA38)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA38)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB38" t="str">
-        <f>IF(ROWS($AB$2:AB38)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB38)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC38">
@@ -14905,15 +15111,15 @@
         <v/>
       </c>
       <c r="Z39" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z39)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA39" t="str">
-        <f>IF(ROWS($AA$2:AA39)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA39)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB39" t="str">
-        <f>IF(ROWS($AB$2:AB39)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB39)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC39">
@@ -15003,15 +15209,15 @@
         <v/>
       </c>
       <c r="Z40" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z40)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA40" t="str">
-        <f>IF(ROWS($AA$2:AA40)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA40)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB40" t="str">
-        <f>IF(ROWS($AB$2:AB40)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB40)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC40">
@@ -15101,15 +15307,15 @@
         <v/>
       </c>
       <c r="Z41" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z41)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA41" t="str">
-        <f>IF(ROWS($AA$2:AA41)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA41)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB41" t="str">
-        <f>IF(ROWS($AB$2:AB41)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB41)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC41">
@@ -15199,15 +15405,15 @@
         <v/>
       </c>
       <c r="Z42" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z42)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA42" t="str">
-        <f>IF(ROWS($AA$2:AA42)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA42)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB42" t="str">
-        <f>IF(ROWS($AB$2:AB42)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB42)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC42">
@@ -15297,15 +15503,15 @@
         <v/>
       </c>
       <c r="Z43" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z43)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA43" t="str">
-        <f>IF(ROWS($AA$2:AA43)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA43)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB43" t="str">
-        <f>IF(ROWS($AB$2:AB43)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB43)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC43">
@@ -15395,15 +15601,15 @@
         <v/>
       </c>
       <c r="Z44" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z44)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA44" t="str">
-        <f>IF(ROWS($AA$2:AA44)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA44)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB44" t="str">
-        <f>IF(ROWS($AB$2:AB44)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB44)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC44">
@@ -15493,15 +15699,15 @@
         <v/>
       </c>
       <c r="Z45" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z45)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA45" t="str">
-        <f>IF(ROWS($AA$2:AA45)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA45)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB45" t="str">
-        <f>IF(ROWS($AB$2:AB45)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB45)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC45">
@@ -15591,15 +15797,15 @@
         <v/>
       </c>
       <c r="Z46" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z46)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA46" t="str">
-        <f>IF(ROWS($AA$2:AA46)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA46)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB46" t="str">
-        <f>IF(ROWS($AB$2:AB46)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB46)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC46">
@@ -15689,15 +15895,15 @@
         <v/>
       </c>
       <c r="Z47" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z47)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA47" t="str">
-        <f>IF(ROWS($AA$2:AA47)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA47)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB47" t="str">
-        <f>IF(ROWS($AB$2:AB47)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB47)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC47">
@@ -15787,15 +15993,15 @@
         <v/>
       </c>
       <c r="Z48" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z48)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA48" t="str">
-        <f>IF(ROWS($AA$2:AA48)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA48)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB48" t="str">
-        <f>IF(ROWS($AB$2:AB48)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB48)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC48">
@@ -15885,15 +16091,15 @@
         <v/>
       </c>
       <c r="Z49" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z49)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA49" t="str">
-        <f>IF(ROWS($AA$2:AA49)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA49)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB49" t="str">
-        <f>IF(ROWS($AB$2:AB49)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB49)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC49">
@@ -15983,15 +16189,15 @@
         <v/>
       </c>
       <c r="Z50" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z50)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA50" t="str">
-        <f>IF(ROWS($AA$2:AA50)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA50)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB50" t="str">
-        <f>IF(ROWS($AB$2:AB50)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB50)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC50">
@@ -16081,15 +16287,15 @@
         <v/>
       </c>
       <c r="Z51" t="str">
-        <f>IFERROR(AGGREGATE(15,6,(ROW(入力!$B$9:$B$58)-ROW(入力!$B$9)+1)/(入力!$B$9:$B$58&lt;&gt;""),ROWS($Z$2:Z51)),"")</f>
+        <f>IFERROR(MATCH(ROW()-1,入力!$N$9:$N$58,0),"")</f>
         <v/>
       </c>
       <c r="AA51" t="str">
-        <f>IF(ROWS($AA$2:AA51)&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROWS($AA$2:AA51)),入力!$L$9:$L$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$L$9:$L$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$L$9:$L$58,ROW()-1),入力!$L$9:$L$58,0),""))</f>
         <v/>
       </c>
       <c r="AB51" t="str">
-        <f>IF(ROWS($AB$2:AB51)&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROWS($AB$2:AB51)),入力!$M$9:$M$58,0),""))</f>
+        <f>IF(ROW()-1&gt;COUNTIF(入力!$M$9:$M$58,"&gt;-9.9E+98"),"",IFERROR(MATCH(LARGE(入力!$M$9:$M$58,ROW()-1),入力!$M$9:$M$58,0),""))</f>
         <v/>
       </c>
       <c r="AC51">
